--- a/数据库/合同模板列表/昂氏公司合同模板2025.1.xlsx
+++ b/数据库/合同模板列表/昂氏公司合同模板2025.1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="8250" windowHeight="9975"/>
+    <workbookView windowWidth="27945" windowHeight="14175"/>
   </bookViews>
   <sheets>
     <sheet name="采购合同" sheetId="1" r:id="rId1"/>
